--- a/ECE.xlsx
+++ b/ECE.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lokes\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ACE7BA-CB96-4187-87B2-EA1E7BF23F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="388">
   <si>
     <t>S No</t>
   </si>
@@ -43,9 +49,6 @@
     <t>REGULAR</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
     <t>2503617810621004</t>
   </si>
   <si>
@@ -1178,12 +1181,15 @@
   </si>
   <si>
     <t>ECE D</t>
+  </si>
+  <si>
+    <t>LOKESHWARAN MV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="165" formatCode="\ dd\-mmm\-yyyy"/>
@@ -1216,7 +1222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1227,6 +1233,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1237,14 +1244,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1282,7 +1292,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1354,7 +1364,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1527,22 +1537,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
-  <sheetFormatPr defaultColWidth="6.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G189"/>
+  <sheetFormatPr defaultColWidth="6.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1565,7 +1575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1573,7 +1583,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -1584,22 +1594,22 @@
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E3" s="3">
         <v>39274</v>
@@ -1607,22 +1617,22 @@
       <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E4" s="3">
         <v>39328</v>
@@ -1630,22 +1640,22 @@
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E5" s="3">
         <v>39492</v>
@@ -1653,22 +1663,22 @@
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="E6" s="3">
         <v>39520</v>
@@ -1676,22 +1686,22 @@
       <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>39415</v>
@@ -1699,22 +1709,22 @@
       <c r="F7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E8" s="3">
         <v>39212</v>
@@ -1722,22 +1732,22 @@
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E9" s="3">
         <v>39536</v>
@@ -1745,22 +1755,22 @@
       <c r="F9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E10" s="3">
         <v>39482</v>
@@ -1768,22 +1778,22 @@
       <c r="F10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E11" s="3">
         <v>39398</v>
@@ -1791,22 +1801,22 @@
       <c r="F11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E12" s="3">
         <v>39542</v>
@@ -1814,22 +1824,22 @@
       <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="E13" s="3">
         <v>39620</v>
@@ -1837,22 +1847,22 @@
       <c r="F13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E14" s="3">
         <v>39433</v>
@@ -1860,22 +1870,22 @@
       <c r="F14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E15" s="3">
         <v>39560</v>
@@ -1883,22 +1893,22 @@
       <c r="F15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="E16" s="3">
         <v>39641</v>
@@ -1906,22 +1916,22 @@
       <c r="F16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="E17" s="3">
         <v>39504</v>
@@ -1929,22 +1939,22 @@
       <c r="F17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="E18" s="3">
         <v>39587</v>
@@ -1952,22 +1962,22 @@
       <c r="F18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E19" s="3">
         <v>39606</v>
@@ -1975,22 +1985,22 @@
       <c r="F19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E20" s="3">
         <v>39150</v>
@@ -1998,22 +2008,22 @@
       <c r="F20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E21" s="3">
         <v>39369</v>
@@ -2021,22 +2031,22 @@
       <c r="F21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E22" s="3">
         <v>39450</v>
@@ -2044,22 +2054,22 @@
       <c r="F22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="E23" s="3">
         <v>39654</v>
@@ -2067,22 +2077,22 @@
       <c r="F23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="E24" s="3">
         <v>39617</v>
@@ -2090,22 +2100,22 @@
       <c r="F24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E25" s="3">
         <v>39401</v>
@@ -2113,22 +2123,22 @@
       <c r="F25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E26" s="3">
         <v>38791</v>
@@ -2136,22 +2146,22 @@
       <c r="F26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E27" s="3">
         <v>39541</v>
@@ -2159,22 +2169,22 @@
       <c r="F27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E28" s="3">
         <v>39678</v>
@@ -2182,22 +2192,22 @@
       <c r="F28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="E29" s="3">
         <v>39316</v>
@@ -2205,22 +2215,22 @@
       <c r="F29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E30" s="3">
         <v>39412</v>
@@ -2228,22 +2238,22 @@
       <c r="F30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="E31" s="3">
         <v>39529</v>
@@ -2251,22 +2261,22 @@
       <c r="F31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E32" s="3">
         <v>39325</v>
@@ -2274,22 +2284,22 @@
       <c r="F32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E33" s="3">
         <v>39342</v>
@@ -2297,22 +2307,22 @@
       <c r="F33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="E34" s="3">
         <v>39633</v>
@@ -2320,22 +2330,22 @@
       <c r="F34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E35" s="3">
         <v>39600</v>
@@ -2343,22 +2353,22 @@
       <c r="F35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="E36" s="3">
         <v>39511</v>
@@ -2366,22 +2376,22 @@
       <c r="F36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="E37" s="3">
         <v>39484</v>
@@ -2389,22 +2399,22 @@
       <c r="F37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="E38" s="3">
         <v>39309</v>
@@ -2412,22 +2422,22 @@
       <c r="F38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E39" s="3">
         <v>39510</v>
@@ -2435,22 +2445,22 @@
       <c r="F39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E40" s="3">
         <v>39511</v>
@@ -2458,22 +2468,22 @@
       <c r="F40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E41" s="3">
         <v>39349</v>
@@ -2481,22 +2491,22 @@
       <c r="F41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="E42" s="3">
         <v>39275</v>
@@ -2504,22 +2514,22 @@
       <c r="F42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E43" s="3">
         <v>39458</v>
@@ -2527,22 +2537,22 @@
       <c r="F43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="E44" s="3">
         <v>39430</v>
@@ -2550,22 +2560,22 @@
       <c r="F44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="E45" s="3">
         <v>39409</v>
@@ -2573,22 +2583,22 @@
       <c r="F45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E46" s="3">
         <v>39417</v>
@@ -2596,22 +2606,22 @@
       <c r="F46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="E47" s="3">
         <v>39585</v>
@@ -2619,22 +2629,22 @@
       <c r="F47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E48" s="3">
         <v>39338</v>
@@ -2642,22 +2652,22 @@
       <c r="F48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="E49" s="3">
         <v>39280</v>
@@ -2665,22 +2675,22 @@
       <c r="F49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E50" s="3">
         <v>39387</v>
@@ -2688,22 +2698,22 @@
       <c r="F50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="E51" s="3">
         <v>39503</v>
@@ -2711,22 +2721,22 @@
       <c r="F51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="E52" s="3">
         <v>39485</v>
@@ -2734,22 +2744,22 @@
       <c r="F52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="E53" s="3">
         <v>39615</v>
@@ -2757,22 +2767,22 @@
       <c r="F53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="E54" s="3">
         <v>39175</v>
@@ -2780,22 +2790,22 @@
       <c r="F54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E55" s="3">
         <v>39584</v>
@@ -2803,22 +2813,22 @@
       <c r="F55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="E56" s="3">
         <v>39392</v>
@@ -2826,22 +2836,22 @@
       <c r="F56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="E57" s="3">
         <v>39644</v>
@@ -2849,22 +2859,22 @@
       <c r="F57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="E58" s="3">
         <v>39389</v>
@@ -2872,22 +2882,22 @@
       <c r="F58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="E59" s="3">
         <v>39348</v>
@@ -2895,22 +2905,22 @@
       <c r="F59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="E60" s="3">
         <v>39354</v>
@@ -2918,22 +2928,22 @@
       <c r="F60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="E61" s="3">
         <v>39528</v>
@@ -2941,22 +2951,22 @@
       <c r="F61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E62" s="3">
         <v>39555</v>
@@ -2964,22 +2974,22 @@
       <c r="F62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="E63" s="3">
         <v>39036</v>
@@ -2987,22 +2997,22 @@
       <c r="F63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E64" s="3">
         <v>39159</v>
@@ -3010,22 +3020,22 @@
       <c r="F64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E65" s="3">
         <v>39536</v>
@@ -3033,22 +3043,22 @@
       <c r="F65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="E66" s="3">
         <v>39337</v>
@@ -3056,22 +3066,22 @@
       <c r="F66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="E67" s="3">
         <v>39400</v>
@@ -3079,22 +3089,22 @@
       <c r="F67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="E68" s="3">
         <v>39536</v>
@@ -3102,22 +3112,22 @@
       <c r="F68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="E69" s="3">
         <v>39211</v>
@@ -3125,22 +3135,22 @@
       <c r="F69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="E70" s="3">
         <v>39503</v>
@@ -3148,22 +3158,22 @@
       <c r="F70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="E71" s="3">
         <v>39373</v>
@@ -3171,22 +3181,22 @@
       <c r="F71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="E72" s="3">
         <v>39149</v>
@@ -3194,22 +3204,22 @@
       <c r="F72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E73" s="3">
         <v>39613</v>
@@ -3217,22 +3227,22 @@
       <c r="F73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="E74" s="3">
         <v>39395</v>
@@ -3240,22 +3250,22 @@
       <c r="F74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G74" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="E75" s="3">
         <v>39002</v>
@@ -3263,22 +3273,22 @@
       <c r="F75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="E76" s="3">
         <v>39413</v>
@@ -3286,22 +3296,22 @@
       <c r="F76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E77" s="3">
         <v>39298</v>
@@ -3309,22 +3319,22 @@
       <c r="F77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="E78" s="3">
         <v>39303</v>
@@ -3332,22 +3342,22 @@
       <c r="F78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E79" s="3">
         <v>39352</v>
@@ -3355,22 +3365,22 @@
       <c r="F79" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="E80" s="3">
         <v>39623</v>
@@ -3378,22 +3388,22 @@
       <c r="F80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G80" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="E81" s="3">
         <v>39432</v>
@@ -3401,22 +3411,22 @@
       <c r="F81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="E82" s="3">
         <v>39413</v>
@@ -3424,22 +3434,22 @@
       <c r="F82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="E83" s="3">
         <v>39514</v>
@@ -3447,22 +3457,22 @@
       <c r="F83" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E84" s="3">
         <v>39401</v>
@@ -3470,22 +3480,22 @@
       <c r="F84" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="E85" s="3">
         <v>39472</v>
@@ -3493,22 +3503,22 @@
       <c r="F85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="E86" s="3">
         <v>39348</v>
@@ -3516,22 +3526,22 @@
       <c r="F86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="E87" s="3">
         <v>39375</v>
@@ -3539,22 +3549,22 @@
       <c r="F87" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="E88" s="3">
         <v>39559</v>
@@ -3562,22 +3572,22 @@
       <c r="F88" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="E89" s="3">
         <v>39562</v>
@@ -3585,22 +3595,22 @@
       <c r="F89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G89" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="E90" s="3">
         <v>39351</v>
@@ -3608,22 +3618,22 @@
       <c r="F90" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="E91" s="3">
         <v>39653</v>
@@ -3631,22 +3641,22 @@
       <c r="F91" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G91" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="E92" s="3">
         <v>39088</v>
@@ -3654,22 +3664,22 @@
       <c r="F92" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G92" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="E93" s="3">
         <v>39354</v>
@@ -3677,22 +3687,22 @@
       <c r="F93" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G93" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G93" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="E94" s="3">
         <v>39580</v>
@@ -3700,22 +3710,22 @@
       <c r="F94" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G94" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="E95" s="3">
         <v>39715</v>
@@ -3723,22 +3733,22 @@
       <c r="F95" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G95" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="E96" s="3">
         <v>39408</v>
@@ -3746,22 +3756,22 @@
       <c r="F96" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G96" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="E97" s="3">
         <v>39584</v>
@@ -3769,22 +3779,22 @@
       <c r="F97" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G97" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G97" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="E98" s="3">
         <v>39373</v>
@@ -3792,22 +3802,22 @@
       <c r="F98" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G98" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="E99" s="3">
         <v>39504</v>
@@ -3815,22 +3825,22 @@
       <c r="F99" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G99" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E100" s="3">
         <v>39466</v>
@@ -3838,22 +3848,22 @@
       <c r="F100" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E101" s="3">
         <v>39494</v>
@@ -3861,22 +3871,22 @@
       <c r="F101" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G101" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="E102" s="3">
         <v>38755</v>
@@ -3884,22 +3894,22 @@
       <c r="F102" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="E103" s="3">
         <v>39274</v>
@@ -3907,22 +3917,22 @@
       <c r="F103" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G103" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="E104" s="3">
         <v>39520</v>
@@ -3930,22 +3940,22 @@
       <c r="F104" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G104" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="E105" s="3">
         <v>39028</v>
@@ -3953,22 +3963,22 @@
       <c r="F105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G105" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="E106" s="3">
         <v>39119</v>
@@ -3976,22 +3986,22 @@
       <c r="F106" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G106" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="E107" s="3">
         <v>39274</v>
@@ -3999,22 +4009,22 @@
       <c r="F107" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G107" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G107" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="E108" s="3">
         <v>39180</v>
@@ -4022,22 +4032,22 @@
       <c r="F108" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G108" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G108" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="E109" s="3">
         <v>39520</v>
@@ -4045,22 +4055,22 @@
       <c r="F109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G109" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G109" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="E110" s="3">
         <v>39399</v>
@@ -4068,22 +4078,22 @@
       <c r="F110" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G110" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="E111" s="3">
         <v>39470</v>
@@ -4091,22 +4101,22 @@
       <c r="F111" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G111" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G111" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="E112" s="3">
         <v>39526</v>
@@ -4114,22 +4124,22 @@
       <c r="F112" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G112" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E113" s="3">
         <v>39308</v>
@@ -4137,22 +4147,22 @@
       <c r="F113" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G113" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G113" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="E114" s="3">
         <v>39585</v>
@@ -4160,22 +4170,22 @@
       <c r="F114" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G114" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G114" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="E115" s="3">
         <v>39174</v>
@@ -4183,22 +4193,22 @@
       <c r="F115" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G115" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="E116" s="3">
         <v>39351</v>
@@ -4206,22 +4216,22 @@
       <c r="F116" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G116" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G116" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="E117" s="3">
         <v>39696</v>
@@ -4229,22 +4239,22 @@
       <c r="F117" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G117" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G117" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="E118" s="3">
         <v>39542</v>
@@ -4252,22 +4262,22 @@
       <c r="F118" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G118" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="E119" s="3">
         <v>39380</v>
@@ -4275,22 +4285,22 @@
       <c r="F119" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G119" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="E120" s="3">
         <v>39013</v>
@@ -4298,22 +4308,22 @@
       <c r="F120" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G120" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G120" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="E121" s="3">
         <v>39471</v>
@@ -4321,22 +4331,22 @@
       <c r="F121" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G121" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G121" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="E122" s="3">
         <v>39319</v>
@@ -4344,22 +4354,22 @@
       <c r="F122" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G122" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G122" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="E123" s="3">
         <v>39374</v>
@@ -4367,22 +4377,22 @@
       <c r="F123" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G123" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G123" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="E124" s="3">
         <v>39388</v>
@@ -4390,22 +4400,22 @@
       <c r="F124" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G124" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="E125" s="3">
         <v>39369</v>
@@ -4413,22 +4423,22 @@
       <c r="F125" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G125" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="E126" s="3">
         <v>39306</v>
@@ -4436,22 +4446,22 @@
       <c r="F126" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G126" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G126" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="E127" s="3">
         <v>39141</v>
@@ -4459,22 +4469,22 @@
       <c r="F127" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G127" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G127" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="E128" s="3">
         <v>39432</v>
@@ -4482,22 +4492,22 @@
       <c r="F128" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G128" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G128" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="E129" s="3">
         <v>39660</v>
@@ -4505,22 +4515,22 @@
       <c r="F129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G129" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G129" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="E130" s="3">
         <v>39305</v>
@@ -4528,22 +4538,22 @@
       <c r="F130" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G130" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G130" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="E131" s="3">
         <v>39347</v>
@@ -4551,22 +4561,22 @@
       <c r="F131" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G131" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G131" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="E132" s="3">
         <v>39593</v>
@@ -4574,22 +4584,22 @@
       <c r="F132" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G132" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G132" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E133" s="3">
         <v>39347</v>
@@ -4597,22 +4607,22 @@
       <c r="F133" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G133" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G133" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="E134" s="3">
         <v>39430</v>
@@ -4620,22 +4630,22 @@
       <c r="F134" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G134" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="E135" s="3">
         <v>39321</v>
@@ -4643,22 +4653,22 @@
       <c r="F135" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G135" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G135" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="E136" s="3">
         <v>39384</v>
@@ -4666,22 +4676,22 @@
       <c r="F136" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G136" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G136" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="E137" s="3">
         <v>39513</v>
@@ -4689,22 +4699,22 @@
       <c r="F137" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G137" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G137" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="E138" s="3">
         <v>39513</v>
@@ -4712,22 +4722,22 @@
       <c r="F138" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G138" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G138" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="E139" s="3">
         <v>39403</v>
@@ -4735,22 +4745,22 @@
       <c r="F139" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G139" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G139" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="E140" s="3">
         <v>39600</v>
@@ -4758,22 +4768,22 @@
       <c r="F140" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G140" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G140" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="E141" s="3">
         <v>39335</v>
@@ -4781,22 +4791,22 @@
       <c r="F141" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G141" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G141" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="E142" s="3">
         <v>39335</v>
@@ -4804,22 +4814,22 @@
       <c r="F142" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G142" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G142" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="E143" s="3">
         <v>39417</v>
@@ -4827,22 +4837,22 @@
       <c r="F143" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G143" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G143" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E144" s="3">
         <v>39335</v>
@@ -4850,22 +4860,22 @@
       <c r="F144" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G144" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G144" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="E145" s="3">
         <v>38927</v>
@@ -4873,22 +4883,22 @@
       <c r="F145" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G145" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G145" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="E146" s="3">
         <v>39364</v>
@@ -4896,22 +4906,22 @@
       <c r="F146" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G146" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G146" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="E147" s="3">
         <v>39360</v>
@@ -4919,22 +4929,22 @@
       <c r="F147" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G147" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G147" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="E148" s="3">
         <v>39386</v>
@@ -4942,22 +4952,22 @@
       <c r="F148" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G148" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G148" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="E149" s="3">
         <v>39392</v>
@@ -4965,22 +4975,22 @@
       <c r="F149" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G149" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G149" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="E150" s="3">
         <v>39535</v>
@@ -4988,22 +4998,22 @@
       <c r="F150" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G150" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G150" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="E151" s="3">
         <v>39458</v>
@@ -5011,22 +5021,22 @@
       <c r="F151" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G151" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G151" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="E152" s="3">
         <v>39506</v>
@@ -5034,22 +5044,22 @@
       <c r="F152" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G152" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G152" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="E153" s="3">
         <v>38386</v>
@@ -5057,22 +5067,22 @@
       <c r="F153" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G153" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G153" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="E154" s="3">
         <v>39562</v>
@@ -5080,22 +5090,22 @@
       <c r="F154" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G154" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G154" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E155" s="3">
         <v>39283</v>
@@ -5103,22 +5113,22 @@
       <c r="F155" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G155" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G155" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="E156" s="3">
         <v>39361</v>
@@ -5126,22 +5136,22 @@
       <c r="F156" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G156" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G156" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="E157" s="3">
         <v>39202</v>
@@ -5149,22 +5159,22 @@
       <c r="F157" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G157" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G157" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="E158" s="3">
         <v>39398</v>
@@ -5172,22 +5182,22 @@
       <c r="F158" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G158" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G158" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="E159" s="3">
         <v>39455</v>
@@ -5195,22 +5205,22 @@
       <c r="F159" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G159" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G159" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="E160" s="3">
         <v>39310</v>
@@ -5218,22 +5228,22 @@
       <c r="F160" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G160" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G160" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="E161" s="3">
         <v>39556</v>
@@ -5241,22 +5251,22 @@
       <c r="F161" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G161" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G161" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="E162" s="3">
         <v>39427</v>
@@ -5264,22 +5274,22 @@
       <c r="F162" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G162" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G162" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="E163" s="3">
         <v>39339</v>
@@ -5287,22 +5297,22 @@
       <c r="F163" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G163" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G163" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="E164" s="3">
         <v>39694</v>
@@ -5310,22 +5320,22 @@
       <c r="F164" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G164" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G164" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="E165" s="3">
         <v>39367</v>
@@ -5333,22 +5343,22 @@
       <c r="F165" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G165" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G165" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="E166" s="3">
         <v>39294</v>
@@ -5356,22 +5366,22 @@
       <c r="F166" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G166" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G166" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="E167" s="3">
         <v>39376</v>
@@ -5379,22 +5389,22 @@
       <c r="F167" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G167" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G167" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="E168" s="3">
         <v>39661</v>
@@ -5402,22 +5412,22 @@
       <c r="F168" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G168" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G168" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="E169" s="3">
         <v>39462</v>
@@ -5425,22 +5435,22 @@
       <c r="F169" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G169" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G169" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="E170" s="3">
         <v>39298</v>
@@ -5448,22 +5458,22 @@
       <c r="F170" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G170" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G170" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="E171" s="3">
         <v>39592</v>
@@ -5471,22 +5481,22 @@
       <c r="F171" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G171" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G171" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="E172" s="3">
         <v>39240</v>
@@ -5494,22 +5504,22 @@
       <c r="F172" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G172" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G172" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="E173" s="3">
         <v>38951</v>
@@ -5517,22 +5527,22 @@
       <c r="F173" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G173" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G173" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="E174" s="3">
         <v>39596</v>
@@ -5540,22 +5550,22 @@
       <c r="F174" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G174" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G174" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="E175" s="3">
         <v>39519</v>
@@ -5563,22 +5573,22 @@
       <c r="F175" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G175" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G175" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="E176" s="3">
         <v>39023</v>
@@ -5586,22 +5596,22 @@
       <c r="F176" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G176" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G176" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="E177" s="3">
         <v>39326</v>
@@ -5609,22 +5619,22 @@
       <c r="F177" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G177" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G177" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="E178" s="3">
         <v>39405</v>
@@ -5632,22 +5642,22 @@
       <c r="F178" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G178" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G178" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="E179" s="3">
         <v>39199</v>
@@ -5655,22 +5665,22 @@
       <c r="F179" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G179" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G179" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E180" s="3">
         <v>39625</v>
@@ -5678,22 +5688,22 @@
       <c r="F180" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G180" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G180" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="E181" s="3">
         <v>39165</v>
@@ -5701,22 +5711,22 @@
       <c r="F181" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G181" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G181" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="E182" s="3">
         <v>39357</v>
@@ -5724,22 +5734,22 @@
       <c r="F182" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G182" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G182" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="E183" s="3">
         <v>39520</v>
@@ -5747,22 +5757,22 @@
       <c r="F183" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G183" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G183" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="E184" s="3">
         <v>39569</v>
@@ -5770,22 +5780,22 @@
       <c r="F184" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G184" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G184" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E185" s="3">
         <v>39547</v>
@@ -5793,22 +5803,22 @@
       <c r="F185" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G185" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G185" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="E186" s="3">
         <v>38727</v>
@@ -5816,22 +5826,22 @@
       <c r="F186" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G186" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G186" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="E187" s="3">
         <v>38525</v>
@@ -5839,22 +5849,22 @@
       <c r="F187" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G187" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G187" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="E188" s="3">
         <v>39427</v>
@@ -5862,8 +5872,31 @@
       <c r="F188" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G188" s="1" t="s">
-        <v>9</v>
+      <c r="G188" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>61782323103085</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E189" s="4">
+        <v>38753</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G189">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/ECE.xlsx
+++ b/ECE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lokes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ACE7BA-CB96-4187-87B2-EA1E7BF23F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4DCB0-6246-4477-A3DD-09B8BFFADBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="390">
   <si>
     <t>S No</t>
   </si>
@@ -1184,6 +1184,12 @@
   </si>
   <si>
     <t>LOKESHWARAN MV</t>
+  </si>
+  <si>
+    <t>JASWANTH B</t>
+  </si>
+  <si>
+    <t>PRATHVIN J</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1234,6 +1240,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1542,7 +1551,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr defaultColWidth="6.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.88671875" customWidth="1"/>
@@ -5880,7 +5889,7 @@
       <c r="A189" s="2">
         <v>188</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="5">
         <v>61782323103085</v>
       </c>
       <c r="C189" s="1" t="s">
@@ -5896,6 +5905,52 @@
         <v>8</v>
       </c>
       <c r="G189">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5">
+        <v>61782323103065</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E190" s="4">
+        <v>38745</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G190" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5">
+        <v>61782323103121</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E191" s="4">
+        <v>38518</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G191" s="1">
         <v>6</v>
       </c>
     </row>

--- a/ECE.xlsx
+++ b/ECE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lokes\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Srinath\Practice Projects\QPapers-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4DCB0-6246-4477-A3DD-09B8BFFADBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C2FAC0-A2DF-42AC-A12C-12D93DA94027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1604,7 +1604,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1627,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1650,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1696,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1719,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1765,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1880,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1903,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1926,7 +1926,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1972,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1995,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2018,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2041,7 +2041,7 @@
         <v>8</v>
       </c>
       <c r="G21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2087,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2110,7 +2110,7 @@
         <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2133,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2179,7 +2179,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2202,7 +2202,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,7 +2248,7 @@
         <v>8</v>
       </c>
       <c r="G30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,7 +2271,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2294,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2363,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2409,7 +2409,7 @@
         <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="G38" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2455,7 +2455,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2478,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="G40" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2501,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="G41" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2547,7 +2547,7 @@
         <v>8</v>
       </c>
       <c r="G43" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2570,7 +2570,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2593,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2616,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2639,7 +2639,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2662,7 +2662,7 @@
         <v>8</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2685,7 +2685,7 @@
         <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2731,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="G51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2754,7 +2754,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2777,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2800,7 +2800,7 @@
         <v>8</v>
       </c>
       <c r="G54" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2823,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2846,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="G56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2869,7 +2869,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="G59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2938,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="G61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2984,7 +2984,7 @@
         <v>8</v>
       </c>
       <c r="G62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3007,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3030,7 +3030,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3053,7 +3053,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3076,7 +3076,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3122,7 +3122,7 @@
         <v>8</v>
       </c>
       <c r="G68" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3145,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,7 +3168,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3191,7 +3191,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3214,7 +3214,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3237,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,7 +3260,7 @@
         <v>8</v>
       </c>
       <c r="G74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3283,7 +3283,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3306,7 +3306,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3329,7 +3329,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3375,7 +3375,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3421,7 +3421,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3444,7 +3444,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3467,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,7 +3490,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3513,7 +3513,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3536,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3559,7 +3559,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3605,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3628,7 +3628,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3651,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,7 +3674,7 @@
         <v>8</v>
       </c>
       <c r="G92" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3697,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,7 +3720,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3743,7 +3743,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3766,7 +3766,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3789,7 +3789,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3812,7 +3812,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3835,7 +3835,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3858,7 +3858,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3881,7 +3881,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3904,7 +3904,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3927,7 +3927,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
         <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>8</v>
       </c>
       <c r="G105" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,7 +3996,7 @@
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>8</v>
       </c>
       <c r="G107" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4042,7 +4042,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4088,7 +4088,7 @@
         <v>8</v>
       </c>
       <c r="G110" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,7 +4111,7 @@
         <v>8</v>
       </c>
       <c r="G111" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4134,7 +4134,7 @@
         <v>8</v>
       </c>
       <c r="G112" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>8</v>
       </c>
       <c r="G113" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4203,7 +4203,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4226,7 +4226,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4249,7 +4249,7 @@
         <v>8</v>
       </c>
       <c r="G117" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4272,7 +4272,7 @@
         <v>8</v>
       </c>
       <c r="G118" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4295,7 +4295,7 @@
         <v>8</v>
       </c>
       <c r="G119" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4318,7 +4318,7 @@
         <v>8</v>
       </c>
       <c r="G120" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>8</v>
       </c>
       <c r="G121" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4364,7 +4364,7 @@
         <v>8</v>
       </c>
       <c r="G122" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4387,7 +4387,7 @@
         <v>8</v>
       </c>
       <c r="G123" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4410,7 +4410,7 @@
         <v>8</v>
       </c>
       <c r="G124" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>8</v>
       </c>
       <c r="G125" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>8</v>
       </c>
       <c r="G126" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4479,7 +4479,7 @@
         <v>8</v>
       </c>
       <c r="G127" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>8</v>
       </c>
       <c r="G128" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>8</v>
       </c>
       <c r="G129" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4548,7 +4548,7 @@
         <v>8</v>
       </c>
       <c r="G130" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4571,7 +4571,7 @@
         <v>8</v>
       </c>
       <c r="G131" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4594,7 +4594,7 @@
         <v>8</v>
       </c>
       <c r="G132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4617,7 +4617,7 @@
         <v>8</v>
       </c>
       <c r="G133" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="G134" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4663,7 +4663,7 @@
         <v>8</v>
       </c>
       <c r="G135" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4686,7 +4686,7 @@
         <v>8</v>
       </c>
       <c r="G136" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
         <v>8</v>
       </c>
       <c r="G137" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4732,7 +4732,7 @@
         <v>8</v>
       </c>
       <c r="G138" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4755,7 +4755,7 @@
         <v>8</v>
       </c>
       <c r="G139" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,7 +4778,7 @@
         <v>8</v>
       </c>
       <c r="G140" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4801,7 +4801,7 @@
         <v>8</v>
       </c>
       <c r="G141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4824,7 +4824,7 @@
         <v>8</v>
       </c>
       <c r="G142" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4847,7 +4847,7 @@
         <v>8</v>
       </c>
       <c r="G143" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4870,7 +4870,7 @@
         <v>8</v>
       </c>
       <c r="G144" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>8</v>
       </c>
       <c r="G145" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4916,7 +4916,7 @@
         <v>8</v>
       </c>
       <c r="G146" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4939,7 +4939,7 @@
         <v>8</v>
       </c>
       <c r="G147" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>8</v>
       </c>
       <c r="G148" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4985,7 +4985,7 @@
         <v>8</v>
       </c>
       <c r="G149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5008,7 +5008,7 @@
         <v>8</v>
       </c>
       <c r="G150" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5031,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="G151" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5054,7 +5054,7 @@
         <v>8</v>
       </c>
       <c r="G152" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5077,7 +5077,7 @@
         <v>8</v>
       </c>
       <c r="G153" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5100,7 +5100,7 @@
         <v>8</v>
       </c>
       <c r="G154" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5123,7 +5123,7 @@
         <v>8</v>
       </c>
       <c r="G155" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
         <v>8</v>
       </c>
       <c r="G156" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5169,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="G157" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5192,7 +5192,7 @@
         <v>8</v>
       </c>
       <c r="G158" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5215,7 +5215,7 @@
         <v>8</v>
       </c>
       <c r="G159" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5238,7 +5238,7 @@
         <v>8</v>
       </c>
       <c r="G160" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5261,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="G161" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>8</v>
       </c>
       <c r="G162" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5307,7 +5307,7 @@
         <v>8</v>
       </c>
       <c r="G163" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5330,7 +5330,7 @@
         <v>8</v>
       </c>
       <c r="G164" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>8</v>
       </c>
       <c r="G165" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5376,7 +5376,7 @@
         <v>8</v>
       </c>
       <c r="G166" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5399,7 +5399,7 @@
         <v>8</v>
       </c>
       <c r="G167" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5422,7 +5422,7 @@
         <v>8</v>
       </c>
       <c r="G168" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5445,7 +5445,7 @@
         <v>8</v>
       </c>
       <c r="G169" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5468,7 +5468,7 @@
         <v>8</v>
       </c>
       <c r="G170" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G171" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5514,7 +5514,7 @@
         <v>8</v>
       </c>
       <c r="G172" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5537,7 +5537,7 @@
         <v>8</v>
       </c>
       <c r="G173" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G174" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5583,7 +5583,7 @@
         <v>8</v>
       </c>
       <c r="G175" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5606,7 +5606,7 @@
         <v>8</v>
       </c>
       <c r="G176" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
         <v>8</v>
       </c>
       <c r="G177" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5652,7 +5652,7 @@
         <v>8</v>
       </c>
       <c r="G178" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5675,7 +5675,7 @@
         <v>8</v>
       </c>
       <c r="G179" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5698,7 +5698,7 @@
         <v>8</v>
       </c>
       <c r="G180" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5721,7 +5721,7 @@
         <v>8</v>
       </c>
       <c r="G181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5744,7 +5744,7 @@
         <v>8</v>
       </c>
       <c r="G182" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5767,7 +5767,7 @@
         <v>8</v>
       </c>
       <c r="G183" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5790,7 +5790,7 @@
         <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>8</v>
       </c>
       <c r="G185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5836,7 +5836,7 @@
         <v>8</v>
       </c>
       <c r="G186" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5859,7 +5859,7 @@
         <v>8</v>
       </c>
       <c r="G187" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5882,7 +5882,7 @@
         <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5905,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="G189">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5927,8 +5927,8 @@
       <c r="F190" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G190" s="1">
-        <v>6</v>
+      <c r="G190">
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5950,8 +5950,8 @@
       <c r="F191" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G191" s="1">
-        <v>6</v>
+      <c r="G191">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
